--- a/Pertemuan 1/Crude Oil Close Price.xlsx
+++ b/Pertemuan 1/Crude Oil Close Price.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KULIAH\Semester 5\DATA SEMESTER 5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3265EA99-ACB6-435B-9D72-F13ADB067147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88EF3CB3-201B-40D5-8C0F-31321F0A3B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{ECAA71A2-6BFE-4FEB-8999-6D635A79EBD9}"/>
   </bookViews>
@@ -31,6 +31,17 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Close</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -64,8 +75,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -380,9 +392,4022 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{333717A7-8E8A-4730-A88F-E6B90FAD2D1E}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B501"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>45293</v>
+      </c>
+      <c r="B2">
+        <v>70.379997253417898</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>45294</v>
+      </c>
+      <c r="B3">
+        <v>72.699996948242102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>45295</v>
+      </c>
+      <c r="B4">
+        <v>72.190002441406193</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>45296</v>
+      </c>
+      <c r="B5">
+        <v>73.809997558593693</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>45299</v>
+      </c>
+      <c r="B6">
+        <v>70.769996643066406</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>45300</v>
+      </c>
+      <c r="B7">
+        <v>72.239997863769503</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>45301</v>
+      </c>
+      <c r="B8">
+        <v>71.370002746582003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>45302</v>
+      </c>
+      <c r="B9">
+        <v>72.019996643066406</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>45303</v>
+      </c>
+      <c r="B10">
+        <v>72.680000305175696</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>45307</v>
+      </c>
+      <c r="B11">
+        <v>72.400001525878906</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>45308</v>
+      </c>
+      <c r="B12">
+        <v>72.559997558593693</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>45309</v>
+      </c>
+      <c r="B13">
+        <v>74.080001831054602</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>45310</v>
+      </c>
+      <c r="B14">
+        <v>73.410003662109304</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>45313</v>
+      </c>
+      <c r="B15">
+        <v>75.190002441406193</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>45314</v>
+      </c>
+      <c r="B16">
+        <v>74.370002746582003</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>45315</v>
+      </c>
+      <c r="B17">
+        <v>75.089996337890597</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>45316</v>
+      </c>
+      <c r="B18">
+        <v>77.360000610351506</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>45317</v>
+      </c>
+      <c r="B19">
+        <v>78.010002136230398</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>45320</v>
+      </c>
+      <c r="B20">
+        <v>76.779998779296804</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>45321</v>
+      </c>
+      <c r="B21">
+        <v>77.819999694824205</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>45322</v>
+      </c>
+      <c r="B22">
+        <v>75.849998474121094</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>45323</v>
+      </c>
+      <c r="B23">
+        <v>73.819999694824205</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>45324</v>
+      </c>
+      <c r="B24">
+        <v>72.279998779296804</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>45327</v>
+      </c>
+      <c r="B25">
+        <v>72.779998779296804</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>45328</v>
+      </c>
+      <c r="B26">
+        <v>73.309997558593693</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>45329</v>
+      </c>
+      <c r="B27">
+        <v>73.860000610351506</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>45330</v>
+      </c>
+      <c r="B28">
+        <v>76.220001220703097</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>45331</v>
+      </c>
+      <c r="B29">
+        <v>76.839996337890597</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>45334</v>
+      </c>
+      <c r="B30">
+        <v>76.919998168945298</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>45335</v>
+      </c>
+      <c r="B31">
+        <v>77.870002746582003</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>45336</v>
+      </c>
+      <c r="B32">
+        <v>76.639999389648395</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>45337</v>
+      </c>
+      <c r="B33">
+        <v>78.029998779296804</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>45338</v>
+      </c>
+      <c r="B34">
+        <v>79.190002441406193</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>45342</v>
+      </c>
+      <c r="B35">
+        <v>78.180000305175696</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>45343</v>
+      </c>
+      <c r="B36">
+        <v>77.910003662109304</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>45344</v>
+      </c>
+      <c r="B37">
+        <v>78.610000610351506</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>45345</v>
+      </c>
+      <c r="B38">
+        <v>76.489997863769503</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>45348</v>
+      </c>
+      <c r="B39">
+        <v>77.580001831054602</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>45349</v>
+      </c>
+      <c r="B40">
+        <v>78.870002746582003</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>45350</v>
+      </c>
+      <c r="B41">
+        <v>78.540000915527301</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>45351</v>
+      </c>
+      <c r="B42">
+        <v>78.260002136230398</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>45352</v>
+      </c>
+      <c r="B43">
+        <v>79.970001220703097</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>45355</v>
+      </c>
+      <c r="B44">
+        <v>78.739997863769503</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>45356</v>
+      </c>
+      <c r="B45">
+        <v>78.150001525878906</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>45357</v>
+      </c>
+      <c r="B46">
+        <v>79.129997253417898</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>45358</v>
+      </c>
+      <c r="B47">
+        <v>78.930000305175696</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>45359</v>
+      </c>
+      <c r="B48">
+        <v>78.010002136230398</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>45362</v>
+      </c>
+      <c r="B49">
+        <v>77.930000305175696</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>45363</v>
+      </c>
+      <c r="B50">
+        <v>77.559997558593693</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>45364</v>
+      </c>
+      <c r="B51">
+        <v>79.720001220703097</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>45365</v>
+      </c>
+      <c r="B52">
+        <v>81.260002136230398</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>45366</v>
+      </c>
+      <c r="B53">
+        <v>81.040000915527301</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>45369</v>
+      </c>
+      <c r="B54">
+        <v>82.720001220703097</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>45370</v>
+      </c>
+      <c r="B55">
+        <v>83.470001220703097</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>45371</v>
+      </c>
+      <c r="B56">
+        <v>81.680000305175696</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>45372</v>
+      </c>
+      <c r="B57">
+        <v>81.069999694824205</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>45373</v>
+      </c>
+      <c r="B58">
+        <v>80.629997253417898</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>45376</v>
+      </c>
+      <c r="B59">
+        <v>81.949996948242102</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>45377</v>
+      </c>
+      <c r="B60">
+        <v>81.620002746582003</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>45378</v>
+      </c>
+      <c r="B61">
+        <v>81.349998474121094</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>45379</v>
+      </c>
+      <c r="B62">
+        <v>83.169998168945298</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>45383</v>
+      </c>
+      <c r="B63">
+        <v>83.709999084472599</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>45384</v>
+      </c>
+      <c r="B64">
+        <v>85.150001525878906</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>45385</v>
+      </c>
+      <c r="B65">
+        <v>85.430000305175696</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>45386</v>
+      </c>
+      <c r="B66">
+        <v>86.589996337890597</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>45387</v>
+      </c>
+      <c r="B67">
+        <v>86.910003662109304</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>45390</v>
+      </c>
+      <c r="B68">
+        <v>86.430000305175696</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>45391</v>
+      </c>
+      <c r="B69">
+        <v>85.230003356933594</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>45392</v>
+      </c>
+      <c r="B70">
+        <v>86.209999084472599</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>45393</v>
+      </c>
+      <c r="B71">
+        <v>85.019996643066406</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>45394</v>
+      </c>
+      <c r="B72">
+        <v>85.660003662109304</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>45397</v>
+      </c>
+      <c r="B73">
+        <v>85.410003662109304</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>45398</v>
+      </c>
+      <c r="B74">
+        <v>85.360000610351506</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>45399</v>
+      </c>
+      <c r="B75">
+        <v>82.690002441406193</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>45400</v>
+      </c>
+      <c r="B76">
+        <v>82.730003356933594</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>45401</v>
+      </c>
+      <c r="B77">
+        <v>83.139999389648395</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
+        <v>45404</v>
+      </c>
+      <c r="B78">
+        <v>82.849998474121094</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
+        <v>45405</v>
+      </c>
+      <c r="B79">
+        <v>83.360000610351506</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="1">
+        <v>45406</v>
+      </c>
+      <c r="B80">
+        <v>82.809997558593693</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="1">
+        <v>45407</v>
+      </c>
+      <c r="B81">
+        <v>83.569999694824205</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
+        <v>45408</v>
+      </c>
+      <c r="B82">
+        <v>83.849998474121094</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>45411</v>
+      </c>
+      <c r="B83">
+        <v>82.629997253417898</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
+        <v>45412</v>
+      </c>
+      <c r="B84">
+        <v>81.930000305175696</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" s="1">
+        <v>45413</v>
+      </c>
+      <c r="B85">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
+        <v>45414</v>
+      </c>
+      <c r="B86">
+        <v>78.949996948242102</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>45415</v>
+      </c>
+      <c r="B87">
+        <v>78.110000610351506</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
+        <v>45418</v>
+      </c>
+      <c r="B88">
+        <v>78.480003356933594</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" s="1">
+        <v>45419</v>
+      </c>
+      <c r="B89">
+        <v>78.379997253417898</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" s="1">
+        <v>45420</v>
+      </c>
+      <c r="B90">
+        <v>78.989997863769503</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" s="1">
+        <v>45421</v>
+      </c>
+      <c r="B91">
+        <v>79.260002136230398</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" s="1">
+        <v>45422</v>
+      </c>
+      <c r="B92">
+        <v>78.260002136230398</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" s="1">
+        <v>45425</v>
+      </c>
+      <c r="B93">
+        <v>79.120002746582003</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
+        <v>45426</v>
+      </c>
+      <c r="B94">
+        <v>78.019996643066406</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" s="1">
+        <v>45427</v>
+      </c>
+      <c r="B95">
+        <v>78.629997253417898</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
+        <v>45428</v>
+      </c>
+      <c r="B96">
+        <v>79.230003356933594</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>45429</v>
+      </c>
+      <c r="B97">
+        <v>80.059997558593693</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>45432</v>
+      </c>
+      <c r="B98">
+        <v>79.800003051757798</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>45433</v>
+      </c>
+      <c r="B99">
+        <v>79.260002136230398</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>45434</v>
+      </c>
+      <c r="B100">
+        <v>77.569999694824205</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" s="1">
+        <v>45435</v>
+      </c>
+      <c r="B101">
+        <v>76.870002746582003</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>45436</v>
+      </c>
+      <c r="B102">
+        <v>77.720001220703097</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>45440</v>
+      </c>
+      <c r="B103">
+        <v>79.830001831054602</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
+        <v>45441</v>
+      </c>
+      <c r="B104">
+        <v>79.230003356933594</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
+        <v>45442</v>
+      </c>
+      <c r="B105">
+        <v>77.910003662109304</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
+        <v>45443</v>
+      </c>
+      <c r="B106">
+        <v>76.989997863769503</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107" s="1">
+        <v>45446</v>
+      </c>
+      <c r="B107">
+        <v>74.220001220703097</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108" s="1">
+        <v>45447</v>
+      </c>
+      <c r="B108">
+        <v>73.25</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109" s="1">
+        <v>45448</v>
+      </c>
+      <c r="B109">
+        <v>74.069999694824205</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" s="1">
+        <v>45449</v>
+      </c>
+      <c r="B110">
+        <v>75.550003051757798</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111" s="1">
+        <v>45450</v>
+      </c>
+      <c r="B111">
+        <v>75.529998779296804</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112" s="1">
+        <v>45453</v>
+      </c>
+      <c r="B112">
+        <v>77.739997863769503</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A113" s="1">
+        <v>45454</v>
+      </c>
+      <c r="B113">
+        <v>77.900001525878906</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114" s="1">
+        <v>45455</v>
+      </c>
+      <c r="B114">
+        <v>78.5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115" s="1">
+        <v>45456</v>
+      </c>
+      <c r="B115">
+        <v>78.620002746582003</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116" s="1">
+        <v>45457</v>
+      </c>
+      <c r="B116">
+        <v>78.449996948242102</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A117" s="1">
+        <v>45460</v>
+      </c>
+      <c r="B117">
+        <v>80.330001831054602</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A118" s="1">
+        <v>45461</v>
+      </c>
+      <c r="B118">
+        <v>81.569999694824205</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A119" s="1">
+        <v>45463</v>
+      </c>
+      <c r="B119">
+        <v>82.169998168945298</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A120" s="1">
+        <v>45464</v>
+      </c>
+      <c r="B120">
+        <v>80.730003356933594</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A121" s="1">
+        <v>45467</v>
+      </c>
+      <c r="B121">
+        <v>81.629997253417898</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A122" s="1">
+        <v>45468</v>
+      </c>
+      <c r="B122">
+        <v>80.830001831054602</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A123" s="1">
+        <v>45469</v>
+      </c>
+      <c r="B123">
+        <v>80.900001525878906</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124" s="1">
+        <v>45470</v>
+      </c>
+      <c r="B124">
+        <v>81.739997863769503</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A125" s="1">
+        <v>45471</v>
+      </c>
+      <c r="B125">
+        <v>81.540000915527301</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A126" s="1">
+        <v>45474</v>
+      </c>
+      <c r="B126">
+        <v>83.379997253417898</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A127" s="1">
+        <v>45475</v>
+      </c>
+      <c r="B127">
+        <v>82.809997558593693</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A128" s="1">
+        <v>45476</v>
+      </c>
+      <c r="B128">
+        <v>83.879997253417898</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A129" s="1">
+        <v>45478</v>
+      </c>
+      <c r="B129">
+        <v>83.160003662109304</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A130" s="1">
+        <v>45481</v>
+      </c>
+      <c r="B130">
+        <v>82.330001831054602</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A131" s="1">
+        <v>45482</v>
+      </c>
+      <c r="B131">
+        <v>81.410003662109304</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A132" s="1">
+        <v>45483</v>
+      </c>
+      <c r="B132">
+        <v>82.099998474121094</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A133" s="1">
+        <v>45484</v>
+      </c>
+      <c r="B133">
+        <v>82.620002746582003</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A134" s="1">
+        <v>45485</v>
+      </c>
+      <c r="B134">
+        <v>82.209999084472599</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A135" s="1">
+        <v>45488</v>
+      </c>
+      <c r="B135">
+        <v>81.910003662109304</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A136" s="1">
+        <v>45489</v>
+      </c>
+      <c r="B136">
+        <v>80.760002136230398</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A137" s="1">
+        <v>45490</v>
+      </c>
+      <c r="B137">
+        <v>82.849998474121094</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A138" s="1">
+        <v>45491</v>
+      </c>
+      <c r="B138">
+        <v>82.819999694824205</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A139" s="1">
+        <v>45492</v>
+      </c>
+      <c r="B139">
+        <v>80.129997253417898</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A140" s="1">
+        <v>45495</v>
+      </c>
+      <c r="B140">
+        <v>79.779998779296804</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A141" s="1">
+        <v>45496</v>
+      </c>
+      <c r="B141">
+        <v>76.959999084472599</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A142" s="1">
+        <v>45497</v>
+      </c>
+      <c r="B142">
+        <v>77.589996337890597</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A143" s="1">
+        <v>45498</v>
+      </c>
+      <c r="B143">
+        <v>78.279998779296804</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A144" s="1">
+        <v>45499</v>
+      </c>
+      <c r="B144">
+        <v>77.160003662109304</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A145" s="1">
+        <v>45502</v>
+      </c>
+      <c r="B145">
+        <v>75.809997558593693</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A146" s="1">
+        <v>45503</v>
+      </c>
+      <c r="B146">
+        <v>74.730003356933594</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A147" s="1">
+        <v>45504</v>
+      </c>
+      <c r="B147">
+        <v>77.910003662109304</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A148" s="1">
+        <v>45505</v>
+      </c>
+      <c r="B148">
+        <v>76.309997558593693</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A149" s="1">
+        <v>45506</v>
+      </c>
+      <c r="B149">
+        <v>73.519996643066406</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A150" s="1">
+        <v>45509</v>
+      </c>
+      <c r="B150">
+        <v>72.940002441406193</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A151" s="1">
+        <v>45510</v>
+      </c>
+      <c r="B151">
+        <v>73.199996948242102</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A152" s="1">
+        <v>45511</v>
+      </c>
+      <c r="B152">
+        <v>75.230003356933594</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A153" s="1">
+        <v>45512</v>
+      </c>
+      <c r="B153">
+        <v>76.190002441406193</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A154" s="1">
+        <v>45513</v>
+      </c>
+      <c r="B154">
+        <v>76.839996337890597</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A155" s="1">
+        <v>45516</v>
+      </c>
+      <c r="B155">
+        <v>80.059997558593693</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A156" s="1">
+        <v>45517</v>
+      </c>
+      <c r="B156">
+        <v>78.349998474121094</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A157" s="1">
+        <v>45518</v>
+      </c>
+      <c r="B157">
+        <v>76.980003356933594</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A158" s="1">
+        <v>45519</v>
+      </c>
+      <c r="B158">
+        <v>78.160003662109304</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A159" s="1">
+        <v>45520</v>
+      </c>
+      <c r="B159">
+        <v>76.650001525878906</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A160" s="1">
+        <v>45523</v>
+      </c>
+      <c r="B160">
+        <v>74.370002746582003</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A161" s="1">
+        <v>45524</v>
+      </c>
+      <c r="B161">
+        <v>74.040000915527301</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A162" s="1">
+        <v>45525</v>
+      </c>
+      <c r="B162">
+        <v>71.930000305175696</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A163" s="1">
+        <v>45526</v>
+      </c>
+      <c r="B163">
+        <v>73.010002136230398</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A164" s="1">
+        <v>45527</v>
+      </c>
+      <c r="B164">
+        <v>74.830001831054602</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A165" s="1">
+        <v>45530</v>
+      </c>
+      <c r="B165">
+        <v>77.419998168945298</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A166" s="1">
+        <v>45531</v>
+      </c>
+      <c r="B166">
+        <v>75.529998779296804</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A167" s="1">
+        <v>45532</v>
+      </c>
+      <c r="B167">
+        <v>74.519996643066406</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A168" s="1">
+        <v>45533</v>
+      </c>
+      <c r="B168">
+        <v>75.910003662109304</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A169" s="1">
+        <v>45534</v>
+      </c>
+      <c r="B169">
+        <v>73.550003051757798</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A170" s="1">
+        <v>45538</v>
+      </c>
+      <c r="B170">
+        <v>70.339996337890597</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A171" s="1">
+        <v>45539</v>
+      </c>
+      <c r="B171">
+        <v>69.199996948242102</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A172" s="1">
+        <v>45540</v>
+      </c>
+      <c r="B172">
+        <v>69.150001525878906</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A173" s="1">
+        <v>45541</v>
+      </c>
+      <c r="B173">
+        <v>67.669998168945298</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A174" s="1">
+        <v>45544</v>
+      </c>
+      <c r="B174">
+        <v>68.709999084472599</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A175" s="1">
+        <v>45545</v>
+      </c>
+      <c r="B175">
+        <v>65.75</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A176" s="1">
+        <v>45546</v>
+      </c>
+      <c r="B176">
+        <v>67.309997558593693</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A177" s="1">
+        <v>45547</v>
+      </c>
+      <c r="B177">
+        <v>68.970001220703097</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A178" s="1">
+        <v>45548</v>
+      </c>
+      <c r="B178">
+        <v>68.650001525878906</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A179" s="1">
+        <v>45551</v>
+      </c>
+      <c r="B179">
+        <v>70.089996337890597</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A180" s="1">
+        <v>45552</v>
+      </c>
+      <c r="B180">
+        <v>71.190002441406193</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A181" s="1">
+        <v>45553</v>
+      </c>
+      <c r="B181">
+        <v>70.910003662109304</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A182" s="1">
+        <v>45554</v>
+      </c>
+      <c r="B182">
+        <v>71.949996948242102</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A183" s="1">
+        <v>45555</v>
+      </c>
+      <c r="B183">
+        <v>71.919998168945298</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A184" s="1">
+        <v>45558</v>
+      </c>
+      <c r="B184">
+        <v>70.370002746582003</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A185" s="1">
+        <v>45559</v>
+      </c>
+      <c r="B185">
+        <v>71.559997558593693</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A186" s="1">
+        <v>45560</v>
+      </c>
+      <c r="B186">
+        <v>69.690002441406193</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A187" s="1">
+        <v>45561</v>
+      </c>
+      <c r="B187">
+        <v>67.669998168945298</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A188" s="1">
+        <v>45562</v>
+      </c>
+      <c r="B188">
+        <v>68.180000305175696</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A189" s="1">
+        <v>45565</v>
+      </c>
+      <c r="B189">
+        <v>68.169998168945298</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A190" s="1">
+        <v>45566</v>
+      </c>
+      <c r="B190">
+        <v>69.830001831054602</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A191" s="1">
+        <v>45567</v>
+      </c>
+      <c r="B191">
+        <v>70.099998474121094</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A192" s="1">
+        <v>45568</v>
+      </c>
+      <c r="B192">
+        <v>73.709999084472599</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A193" s="1">
+        <v>45569</v>
+      </c>
+      <c r="B193">
+        <v>74.379997253417898</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A194" s="1">
+        <v>45572</v>
+      </c>
+      <c r="B194">
+        <v>77.139999389648395</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A195" s="1">
+        <v>45573</v>
+      </c>
+      <c r="B195">
+        <v>73.569999694824205</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A196" s="1">
+        <v>45574</v>
+      </c>
+      <c r="B196">
+        <v>73.239997863769503</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A197" s="1">
+        <v>45575</v>
+      </c>
+      <c r="B197">
+        <v>75.849998474121094</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A198" s="1">
+        <v>45576</v>
+      </c>
+      <c r="B198">
+        <v>75.559997558593693</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A199" s="1">
+        <v>45579</v>
+      </c>
+      <c r="B199">
+        <v>73.830001831054602</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A200" s="1">
+        <v>45580</v>
+      </c>
+      <c r="B200">
+        <v>70.580001831054602</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A201" s="1">
+        <v>45581</v>
+      </c>
+      <c r="B201">
+        <v>70.389999389648395</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A202" s="1">
+        <v>45582</v>
+      </c>
+      <c r="B202">
+        <v>70.669998168945298</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A203" s="1">
+        <v>45583</v>
+      </c>
+      <c r="B203">
+        <v>69.220001220703097</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A204" s="1">
+        <v>45586</v>
+      </c>
+      <c r="B204">
+        <v>70.559997558593693</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A205" s="1">
+        <v>45587</v>
+      </c>
+      <c r="B205">
+        <v>72.089996337890597</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A206" s="1">
+        <v>45588</v>
+      </c>
+      <c r="B206">
+        <v>70.769996643066406</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A207" s="1">
+        <v>45589</v>
+      </c>
+      <c r="B207">
+        <v>70.190002441406193</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A208" s="1">
+        <v>45590</v>
+      </c>
+      <c r="B208">
+        <v>71.779998779296804</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A209" s="1">
+        <v>45593</v>
+      </c>
+      <c r="B209">
+        <v>67.379997253417898</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A210" s="1">
+        <v>45594</v>
+      </c>
+      <c r="B210">
+        <v>67.209999084472599</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A211" s="1">
+        <v>45595</v>
+      </c>
+      <c r="B211">
+        <v>68.610000610351506</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A212" s="1">
+        <v>45596</v>
+      </c>
+      <c r="B212">
+        <v>69.260002136230398</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A213" s="1">
+        <v>45597</v>
+      </c>
+      <c r="B213">
+        <v>69.489997863769503</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A214" s="1">
+        <v>45600</v>
+      </c>
+      <c r="B214">
+        <v>71.470001220703097</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A215" s="1">
+        <v>45601</v>
+      </c>
+      <c r="B215">
+        <v>71.989997863769503</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A216" s="1">
+        <v>45602</v>
+      </c>
+      <c r="B216">
+        <v>71.690002441406193</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A217" s="1">
+        <v>45603</v>
+      </c>
+      <c r="B217">
+        <v>72.360000610351506</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A218" s="1">
+        <v>45604</v>
+      </c>
+      <c r="B218">
+        <v>70.379997253417898</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A219" s="1">
+        <v>45607</v>
+      </c>
+      <c r="B219">
+        <v>68.040000915527301</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A220" s="1">
+        <v>45608</v>
+      </c>
+      <c r="B220">
+        <v>68.120002746582003</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A221" s="1">
+        <v>45609</v>
+      </c>
+      <c r="B221">
+        <v>68.430000305175696</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A222" s="1">
+        <v>45610</v>
+      </c>
+      <c r="B222">
+        <v>68.699996948242102</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A223" s="1">
+        <v>45611</v>
+      </c>
+      <c r="B223">
+        <v>67.019996643066406</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A224" s="1">
+        <v>45614</v>
+      </c>
+      <c r="B224">
+        <v>69.160003662109304</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A225" s="1">
+        <v>45615</v>
+      </c>
+      <c r="B225">
+        <v>69.389999389648395</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A226" s="1">
+        <v>45616</v>
+      </c>
+      <c r="B226">
+        <v>68.870002746582003</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A227" s="1">
+        <v>45617</v>
+      </c>
+      <c r="B227">
+        <v>70.099998474121094</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A228" s="1">
+        <v>45618</v>
+      </c>
+      <c r="B228">
+        <v>71.239997863769503</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A229" s="1">
+        <v>45621</v>
+      </c>
+      <c r="B229">
+        <v>68.940002441406193</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A230" s="1">
+        <v>45622</v>
+      </c>
+      <c r="B230">
+        <v>68.769996643066406</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A231" s="1">
+        <v>45623</v>
+      </c>
+      <c r="B231">
+        <v>68.720001220703097</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A232" s="1">
+        <v>45625</v>
+      </c>
+      <c r="B232">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A233" s="1">
+        <v>45628</v>
+      </c>
+      <c r="B233">
+        <v>68.099998474121094</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A234" s="1">
+        <v>45629</v>
+      </c>
+      <c r="B234">
+        <v>69.940002441406193</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A235" s="1">
+        <v>45630</v>
+      </c>
+      <c r="B235">
+        <v>68.540000915527301</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A236" s="1">
+        <v>45631</v>
+      </c>
+      <c r="B236">
+        <v>68.300003051757798</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A237" s="1">
+        <v>45632</v>
+      </c>
+      <c r="B237">
+        <v>67.199996948242102</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A238" s="1">
+        <v>45635</v>
+      </c>
+      <c r="B238">
+        <v>68.370002746582003</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A239" s="1">
+        <v>45636</v>
+      </c>
+      <c r="B239">
+        <v>68.589996337890597</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A240" s="1">
+        <v>45637</v>
+      </c>
+      <c r="B240">
+        <v>70.290000915527301</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A241" s="1">
+        <v>45638</v>
+      </c>
+      <c r="B241">
+        <v>70.019996643066406</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A242" s="1">
+        <v>45639</v>
+      </c>
+      <c r="B242">
+        <v>71.290000915527301</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A243" s="1">
+        <v>45642</v>
+      </c>
+      <c r="B243">
+        <v>70.709999084472599</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A244" s="1">
+        <v>45643</v>
+      </c>
+      <c r="B244">
+        <v>70.080001831054602</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A245" s="1">
+        <v>45644</v>
+      </c>
+      <c r="B245">
+        <v>70.580001831054602</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A246" s="1">
+        <v>45645</v>
+      </c>
+      <c r="B246">
+        <v>69.910003662109304</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A247" s="1">
+        <v>45646</v>
+      </c>
+      <c r="B247">
+        <v>69.459999084472599</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A248" s="1">
+        <v>45649</v>
+      </c>
+      <c r="B248">
+        <v>69.239997863769503</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A249" s="1">
+        <v>45650</v>
+      </c>
+      <c r="B249">
+        <v>70.099998474121094</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A250" s="1">
+        <v>45652</v>
+      </c>
+      <c r="B250">
+        <v>69.620002746582003</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A251" s="1">
+        <v>45653</v>
+      </c>
+      <c r="B251">
+        <v>70.599998474121094</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A252" s="1">
+        <v>45656</v>
+      </c>
+      <c r="B252">
+        <v>70.989997863769503</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A253" s="1">
+        <v>45657</v>
+      </c>
+      <c r="B253">
+        <v>71.720001220703097</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A254" s="1">
+        <v>45659</v>
+      </c>
+      <c r="B254">
+        <v>73.129997253417898</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A255" s="1">
+        <v>45660</v>
+      </c>
+      <c r="B255">
+        <v>73.959999084472599</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A256" s="1">
+        <v>45663</v>
+      </c>
+      <c r="B256">
+        <v>73.559997558593693</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A257" s="1">
+        <v>45664</v>
+      </c>
+      <c r="B257">
+        <v>74.25</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A258" s="1">
+        <v>45665</v>
+      </c>
+      <c r="B258">
+        <v>73.319999694824205</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A259" s="1">
+        <v>45666</v>
+      </c>
+      <c r="B259">
+        <v>73.919998168945298</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A260" s="1">
+        <v>45667</v>
+      </c>
+      <c r="B260">
+        <v>76.569999694824205</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A261" s="1">
+        <v>45670</v>
+      </c>
+      <c r="B261">
+        <v>78.819999694824205</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A262" s="1">
+        <v>45671</v>
+      </c>
+      <c r="B262">
+        <v>77.5</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A263" s="1">
+        <v>45672</v>
+      </c>
+      <c r="B263">
+        <v>80.040000915527301</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A264" s="1">
+        <v>45673</v>
+      </c>
+      <c r="B264">
+        <v>78.680000305175696</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A265" s="1">
+        <v>45674</v>
+      </c>
+      <c r="B265">
+        <v>77.879997253417898</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A266" s="1">
+        <v>45678</v>
+      </c>
+      <c r="B266">
+        <v>75.889999389648395</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A267" s="1">
+        <v>45679</v>
+      </c>
+      <c r="B267">
+        <v>75.440002441406193</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A268" s="1">
+        <v>45680</v>
+      </c>
+      <c r="B268">
+        <v>74.620002746582003</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A269" s="1">
+        <v>45681</v>
+      </c>
+      <c r="B269">
+        <v>74.660003662109304</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A270" s="1">
+        <v>45684</v>
+      </c>
+      <c r="B270">
+        <v>73.169998168945298</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A271" s="1">
+        <v>45685</v>
+      </c>
+      <c r="B271">
+        <v>73.769996643066406</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A272" s="1">
+        <v>45686</v>
+      </c>
+      <c r="B272">
+        <v>72.620002746582003</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A273" s="1">
+        <v>45687</v>
+      </c>
+      <c r="B273">
+        <v>72.730003356933594</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A274" s="1">
+        <v>45688</v>
+      </c>
+      <c r="B274">
+        <v>72.529998779296804</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A275" s="1">
+        <v>45691</v>
+      </c>
+      <c r="B275">
+        <v>73.160003662109304</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A276" s="1">
+        <v>45692</v>
+      </c>
+      <c r="B276">
+        <v>72.699996948242102</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A277" s="1">
+        <v>45693</v>
+      </c>
+      <c r="B277">
+        <v>71.029998779296804</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A278" s="1">
+        <v>45694</v>
+      </c>
+      <c r="B278">
+        <v>70.610000610351506</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A279" s="1">
+        <v>45695</v>
+      </c>
+      <c r="B279">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A280" s="1">
+        <v>45698</v>
+      </c>
+      <c r="B280">
+        <v>72.319999694824205</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A281" s="1">
+        <v>45699</v>
+      </c>
+      <c r="B281">
+        <v>73.319999694824205</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A282" s="1">
+        <v>45700</v>
+      </c>
+      <c r="B282">
+        <v>71.370002746582003</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A283" s="1">
+        <v>45701</v>
+      </c>
+      <c r="B283">
+        <v>71.290000915527301</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A284" s="1">
+        <v>45702</v>
+      </c>
+      <c r="B284">
+        <v>70.739997863769503</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A285" s="1">
+        <v>45706</v>
+      </c>
+      <c r="B285">
+        <v>71.849998474121094</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A286" s="1">
+        <v>45707</v>
+      </c>
+      <c r="B286">
+        <v>72.25</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A287" s="1">
+        <v>45708</v>
+      </c>
+      <c r="B287">
+        <v>72.569999694824205</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A288" s="1">
+        <v>45709</v>
+      </c>
+      <c r="B288">
+        <v>70.400001525878906</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A289" s="1">
+        <v>45712</v>
+      </c>
+      <c r="B289">
+        <v>70.699996948242102</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A290" s="1">
+        <v>45713</v>
+      </c>
+      <c r="B290">
+        <v>68.930000305175696</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A291" s="1">
+        <v>45714</v>
+      </c>
+      <c r="B291">
+        <v>68.620002746582003</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A292" s="1">
+        <v>45715</v>
+      </c>
+      <c r="B292">
+        <v>70.349998474121094</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A293" s="1">
+        <v>45716</v>
+      </c>
+      <c r="B293">
+        <v>69.760002136230398</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A294" s="1">
+        <v>45719</v>
+      </c>
+      <c r="B294">
+        <v>68.370002746582003</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A295" s="1">
+        <v>45720</v>
+      </c>
+      <c r="B295">
+        <v>68.260002136230398</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A296" s="1">
+        <v>45721</v>
+      </c>
+      <c r="B296">
+        <v>66.309997558593693</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A297" s="1">
+        <v>45722</v>
+      </c>
+      <c r="B297">
+        <v>66.360000610351506</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A298" s="1">
+        <v>45723</v>
+      </c>
+      <c r="B298">
+        <v>67.040000915527301</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A299" s="1">
+        <v>45726</v>
+      </c>
+      <c r="B299">
+        <v>66.029998779296804</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A300" s="1">
+        <v>45727</v>
+      </c>
+      <c r="B300">
+        <v>66.25</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A301" s="1">
+        <v>45728</v>
+      </c>
+      <c r="B301">
+        <v>67.680000305175696</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A302" s="1">
+        <v>45729</v>
+      </c>
+      <c r="B302">
+        <v>66.550003051757798</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A303" s="1">
+        <v>45730</v>
+      </c>
+      <c r="B303">
+        <v>67.180000305175696</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A304" s="1">
+        <v>45733</v>
+      </c>
+      <c r="B304">
+        <v>67.580001831054602</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A305" s="1">
+        <v>45734</v>
+      </c>
+      <c r="B305">
+        <v>66.900001525878906</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A306" s="1">
+        <v>45735</v>
+      </c>
+      <c r="B306">
+        <v>67.160003662109304</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A307" s="1">
+        <v>45736</v>
+      </c>
+      <c r="B307">
+        <v>68.260002136230398</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A308" s="1">
+        <v>45737</v>
+      </c>
+      <c r="B308">
+        <v>68.279998779296804</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A309" s="1">
+        <v>45740</v>
+      </c>
+      <c r="B309">
+        <v>69.110000610351506</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A310" s="1">
+        <v>45741</v>
+      </c>
+      <c r="B310">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A311" s="1">
+        <v>45742</v>
+      </c>
+      <c r="B311">
+        <v>69.650001525878906</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A312" s="1">
+        <v>45743</v>
+      </c>
+      <c r="B312">
+        <v>69.919998168945298</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A313" s="1">
+        <v>45744</v>
+      </c>
+      <c r="B313">
+        <v>69.360000610351506</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A314" s="1">
+        <v>45747</v>
+      </c>
+      <c r="B314">
+        <v>71.480003356933594</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A315" s="1">
+        <v>45748</v>
+      </c>
+      <c r="B315">
+        <v>71.199996948242102</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A316" s="1">
+        <v>45749</v>
+      </c>
+      <c r="B316">
+        <v>71.709999084472599</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A317" s="1">
+        <v>45750</v>
+      </c>
+      <c r="B317">
+        <v>66.949996948242102</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A318" s="1">
+        <v>45751</v>
+      </c>
+      <c r="B318">
+        <v>61.990001678466797</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A319" s="1">
+        <v>45754</v>
+      </c>
+      <c r="B319">
+        <v>60.700000762939403</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A320" s="1">
+        <v>45755</v>
+      </c>
+      <c r="B320">
+        <v>59.580001831054602</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A321" s="1">
+        <v>45756</v>
+      </c>
+      <c r="B321">
+        <v>62.349998474121001</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A322" s="1">
+        <v>45757</v>
+      </c>
+      <c r="B322">
+        <v>60.069999694824197</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A323" s="1">
+        <v>45758</v>
+      </c>
+      <c r="B323">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A324" s="1">
+        <v>45761</v>
+      </c>
+      <c r="B324">
+        <v>61.529998779296797</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A325" s="1">
+        <v>45762</v>
+      </c>
+      <c r="B325">
+        <v>61.330001831054602</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A326" s="1">
+        <v>45763</v>
+      </c>
+      <c r="B326">
+        <v>62.470001220703097</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A327" s="1">
+        <v>45764</v>
+      </c>
+      <c r="B327">
+        <v>64.680000305175696</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A328" s="1">
+        <v>45768</v>
+      </c>
+      <c r="B328">
+        <v>63.080001831054602</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A329" s="1">
+        <v>45769</v>
+      </c>
+      <c r="B329">
+        <v>64.309997558593693</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A330" s="1">
+        <v>45770</v>
+      </c>
+      <c r="B330">
+        <v>62.270000457763601</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A331" s="1">
+        <v>45771</v>
+      </c>
+      <c r="B331">
+        <v>62.790000915527301</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A332" s="1">
+        <v>45772</v>
+      </c>
+      <c r="B332">
+        <v>63.020000457763601</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A333" s="1">
+        <v>45775</v>
+      </c>
+      <c r="B333">
+        <v>62.049999237060497</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A334" s="1">
+        <v>45776</v>
+      </c>
+      <c r="B334">
+        <v>60.419998168945298</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A335" s="1">
+        <v>45777</v>
+      </c>
+      <c r="B335">
+        <v>58.209999084472599</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A336" s="1">
+        <v>45778</v>
+      </c>
+      <c r="B336">
+        <v>59.240001678466797</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A337" s="1">
+        <v>45779</v>
+      </c>
+      <c r="B337">
+        <v>58.290000915527301</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A338" s="1">
+        <v>45782</v>
+      </c>
+      <c r="B338">
+        <v>57.130001068115199</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A339" s="1">
+        <v>45783</v>
+      </c>
+      <c r="B339">
+        <v>59.090000152587798</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A340" s="1">
+        <v>45784</v>
+      </c>
+      <c r="B340">
+        <v>58.069999694824197</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A341" s="1">
+        <v>45785</v>
+      </c>
+      <c r="B341">
+        <v>59.909999847412102</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A342" s="1">
+        <v>45786</v>
+      </c>
+      <c r="B342">
+        <v>61.020000457763601</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A343" s="1">
+        <v>45789</v>
+      </c>
+      <c r="B343">
+        <v>61.950000762939403</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A344" s="1">
+        <v>45790</v>
+      </c>
+      <c r="B344">
+        <v>63.669998168945298</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A345" s="1">
+        <v>45791</v>
+      </c>
+      <c r="B345">
+        <v>63.150001525878899</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A346" s="1">
+        <v>45792</v>
+      </c>
+      <c r="B346">
+        <v>61.619998931884702</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A347" s="1">
+        <v>45793</v>
+      </c>
+      <c r="B347">
+        <v>62.490001678466797</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A348" s="1">
+        <v>45796</v>
+      </c>
+      <c r="B348">
+        <v>62.689998626708899</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A349" s="1">
+        <v>45797</v>
+      </c>
+      <c r="B349">
+        <v>62.560001373291001</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A350" s="1">
+        <v>45798</v>
+      </c>
+      <c r="B350">
+        <v>61.569999694824197</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A351" s="1">
+        <v>45799</v>
+      </c>
+      <c r="B351">
+        <v>61.200000762939403</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A352" s="1">
+        <v>45800</v>
+      </c>
+      <c r="B352">
+        <v>61.529998779296797</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A353" s="1">
+        <v>45804</v>
+      </c>
+      <c r="B353">
+        <v>60.889999389648402</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A354" s="1">
+        <v>45805</v>
+      </c>
+      <c r="B354">
+        <v>61.840000152587798</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A355" s="1">
+        <v>45806</v>
+      </c>
+      <c r="B355">
+        <v>60.939998626708899</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A356" s="1">
+        <v>45807</v>
+      </c>
+      <c r="B356">
+        <v>60.790000915527301</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A357" s="1">
+        <v>45810</v>
+      </c>
+      <c r="B357">
+        <v>62.520000457763601</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A358" s="1">
+        <v>45811</v>
+      </c>
+      <c r="B358">
+        <v>63.409999847412102</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A359" s="1">
+        <v>45812</v>
+      </c>
+      <c r="B359">
+        <v>62.849998474121001</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A360" s="1">
+        <v>45813</v>
+      </c>
+      <c r="B360">
+        <v>63.369998931884702</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A361" s="1">
+        <v>45814</v>
+      </c>
+      <c r="B361">
+        <v>64.580001831054602</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A362" s="1">
+        <v>45817</v>
+      </c>
+      <c r="B362">
+        <v>65.290000915527301</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A363" s="1">
+        <v>45818</v>
+      </c>
+      <c r="B363">
+        <v>64.980003356933594</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A364" s="1">
+        <v>45819</v>
+      </c>
+      <c r="B364">
+        <v>68.150001525878906</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A365" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B365">
+        <v>68.040000915527301</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A366" s="1">
+        <v>45821</v>
+      </c>
+      <c r="B366">
+        <v>72.980003356933594</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A367" s="1">
+        <v>45824</v>
+      </c>
+      <c r="B367">
+        <v>71.769996643066406</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A368" s="1">
+        <v>45825</v>
+      </c>
+      <c r="B368">
+        <v>74.839996337890597</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A369" s="1">
+        <v>45826</v>
+      </c>
+      <c r="B369">
+        <v>75.139999389648395</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A370" s="1">
+        <v>45828</v>
+      </c>
+      <c r="B370">
+        <v>74.930000305175696</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A371" s="1">
+        <v>45831</v>
+      </c>
+      <c r="B371">
+        <v>68.510002136230398</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A372" s="1">
+        <v>45832</v>
+      </c>
+      <c r="B372">
+        <v>64.370002746582003</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A373" s="1">
+        <v>45833</v>
+      </c>
+      <c r="B373">
+        <v>64.919998168945298</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A374" s="1">
+        <v>45834</v>
+      </c>
+      <c r="B374">
+        <v>65.239997863769503</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A375" s="1">
+        <v>45835</v>
+      </c>
+      <c r="B375">
+        <v>65.519996643066406</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A376" s="1">
+        <v>45838</v>
+      </c>
+      <c r="B376">
+        <v>65.110000610351506</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A377" s="1">
+        <v>45839</v>
+      </c>
+      <c r="B377">
+        <v>65.449996948242102</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A378" s="1">
+        <v>45840</v>
+      </c>
+      <c r="B378">
+        <v>67.449996948242102</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A379" s="1">
+        <v>45841</v>
+      </c>
+      <c r="B379">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A380" s="1">
+        <v>45842</v>
+      </c>
+      <c r="B380">
+        <v>66.5</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A381" s="1">
+        <v>45845</v>
+      </c>
+      <c r="B381">
+        <v>67.930000305175696</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A382" s="1">
+        <v>45846</v>
+      </c>
+      <c r="B382">
+        <v>68.330001831054602</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A383" s="1">
+        <v>45847</v>
+      </c>
+      <c r="B383">
+        <v>68.379997253417898</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A384" s="1">
+        <v>45848</v>
+      </c>
+      <c r="B384">
+        <v>66.569999694824205</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A385" s="1">
+        <v>45849</v>
+      </c>
+      <c r="B385">
+        <v>68.449996948242102</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A386" s="1">
+        <v>45852</v>
+      </c>
+      <c r="B386">
+        <v>66.980003356933594</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A387" s="1">
+        <v>45853</v>
+      </c>
+      <c r="B387">
+        <v>66.519996643066406</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A388" s="1">
+        <v>45854</v>
+      </c>
+      <c r="B388">
+        <v>66.379997253417898</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A389" s="1">
+        <v>45855</v>
+      </c>
+      <c r="B389">
+        <v>67.540000915527301</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A390" s="1">
+        <v>45856</v>
+      </c>
+      <c r="B390">
+        <v>67.339996337890597</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A391" s="1">
+        <v>45859</v>
+      </c>
+      <c r="B391">
+        <v>67.199996948242102</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A392" s="1">
+        <v>45860</v>
+      </c>
+      <c r="B392">
+        <v>66.209999084472599</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A393" s="1">
+        <v>45861</v>
+      </c>
+      <c r="B393">
+        <v>65.25</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A394" s="1">
+        <v>45862</v>
+      </c>
+      <c r="B394">
+        <v>66.029998779296804</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A395" s="1">
+        <v>45863</v>
+      </c>
+      <c r="B395">
+        <v>65.160003662109304</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A396" s="1">
+        <v>45866</v>
+      </c>
+      <c r="B396">
+        <v>66.709999084472599</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A397" s="1">
+        <v>45867</v>
+      </c>
+      <c r="B397">
+        <v>69.209999084472599</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A398" s="1">
+        <v>45868</v>
+      </c>
+      <c r="B398">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A399" s="1">
+        <v>45869</v>
+      </c>
+      <c r="B399">
+        <v>69.260002136230398</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A400" s="1">
+        <v>45870</v>
+      </c>
+      <c r="B400">
+        <v>67.330001831054602</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A401" s="1">
+        <v>45873</v>
+      </c>
+      <c r="B401">
+        <v>66.290000915527301</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A402" s="1">
+        <v>45874</v>
+      </c>
+      <c r="B402">
+        <v>65.160003662109304</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A403" s="1">
+        <v>45875</v>
+      </c>
+      <c r="B403">
+        <v>64.349998474121094</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A404" s="1">
+        <v>45876</v>
+      </c>
+      <c r="B404">
+        <v>63.880001068115199</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A405" s="1">
+        <v>45877</v>
+      </c>
+      <c r="B405">
+        <v>63.880001068115199</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A406" s="1">
+        <v>45880</v>
+      </c>
+      <c r="B406">
+        <v>63.959999084472599</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A407" s="1">
+        <v>45881</v>
+      </c>
+      <c r="B407">
+        <v>63.169998168945298</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A408" s="1">
+        <v>45882</v>
+      </c>
+      <c r="B408">
+        <v>62.650001525878899</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A409" s="1">
+        <v>45883</v>
+      </c>
+      <c r="B409">
+        <v>63.959999084472599</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A410" s="1">
+        <v>45884</v>
+      </c>
+      <c r="B410">
+        <v>62.799999237060497</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A411" s="1">
+        <v>45887</v>
+      </c>
+      <c r="B411">
+        <v>63.419998168945298</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A412" s="1">
+        <v>45888</v>
+      </c>
+      <c r="B412">
+        <v>62.349998474121001</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A413" s="1">
+        <v>45889</v>
+      </c>
+      <c r="B413">
+        <v>63.209999084472599</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A414" s="1">
+        <v>45890</v>
+      </c>
+      <c r="B414">
+        <v>63.520000457763601</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A415" s="1">
+        <v>45891</v>
+      </c>
+      <c r="B415">
+        <v>63.659999847412102</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A416" s="1">
+        <v>45894</v>
+      </c>
+      <c r="B416">
+        <v>64.800003051757798</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A417" s="1">
+        <v>45895</v>
+      </c>
+      <c r="B417">
+        <v>63.25</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A418" s="1">
+        <v>45896</v>
+      </c>
+      <c r="B418">
+        <v>64.150001525878906</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A419" s="1">
+        <v>45897</v>
+      </c>
+      <c r="B419">
+        <v>64.599998474121094</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A420" s="1">
+        <v>45898</v>
+      </c>
+      <c r="B420">
+        <v>64.010002136230398</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A421" s="1">
+        <v>45902</v>
+      </c>
+      <c r="B421">
+        <v>65.589996337890597</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A422" s="1">
+        <v>45903</v>
+      </c>
+      <c r="B422">
+        <v>63.970001220703097</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A423" s="1">
+        <v>45904</v>
+      </c>
+      <c r="B423">
+        <v>63.4799995422363</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A424" s="1">
+        <v>45905</v>
+      </c>
+      <c r="B424">
+        <v>61.869998931884702</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A425" s="1">
+        <v>45908</v>
+      </c>
+      <c r="B425">
+        <v>62.259998321533203</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A426" s="1">
+        <v>45909</v>
+      </c>
+      <c r="B426">
+        <v>62.630001068115199</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A427" s="1">
+        <v>45910</v>
+      </c>
+      <c r="B427">
+        <v>63.669998168945298</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A428" s="1">
+        <v>45911</v>
+      </c>
+      <c r="B428">
+        <v>62.369998931884702</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A429" s="1">
+        <v>45912</v>
+      </c>
+      <c r="B429">
+        <v>62.689998626708899</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A430" s="1">
+        <v>45915</v>
+      </c>
+      <c r="B430">
+        <v>63.299999237060497</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A431" s="1">
+        <v>45916</v>
+      </c>
+      <c r="B431">
+        <v>64.519996643066406</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A432" s="1">
+        <v>45917</v>
+      </c>
+      <c r="B432">
+        <v>64.050003051757798</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A433" s="1">
+        <v>45918</v>
+      </c>
+      <c r="B433">
+        <v>63.569999694824197</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A434" s="1">
+        <v>45919</v>
+      </c>
+      <c r="B434">
+        <v>62.680000305175703</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A435" s="1">
+        <v>45922</v>
+      </c>
+      <c r="B435">
+        <v>62.639999389648402</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A436" s="1">
+        <v>45923</v>
+      </c>
+      <c r="B436">
+        <v>63.409999847412102</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A437" s="1">
+        <v>45924</v>
+      </c>
+      <c r="B437">
+        <v>64.989997863769503</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A438" s="1">
+        <v>45925</v>
+      </c>
+      <c r="B438">
+        <v>64.980003356933594</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A439" s="1">
+        <v>45926</v>
+      </c>
+      <c r="B439">
+        <v>65.720001220703097</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A440" s="1">
+        <v>45929</v>
+      </c>
+      <c r="B440">
+        <v>63.450000762939403</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A441" s="1">
+        <v>45930</v>
+      </c>
+      <c r="B441">
+        <v>62.369998931884702</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A442" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B442">
+        <v>61.779998779296797</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A443" s="1">
+        <v>45932</v>
+      </c>
+      <c r="B443">
+        <v>60.4799995422363</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A444" s="1">
+        <v>45933</v>
+      </c>
+      <c r="B444">
+        <v>60.880001068115199</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A445" s="1">
+        <v>45936</v>
+      </c>
+      <c r="B445">
+        <v>61.689998626708899</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A446" s="1">
+        <v>45937</v>
+      </c>
+      <c r="B446">
+        <v>61.7299995422363</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A447" s="1">
+        <v>45938</v>
+      </c>
+      <c r="B447">
+        <v>62.549999237060497</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A448" s="1">
+        <v>45939</v>
+      </c>
+      <c r="B448">
+        <v>61.509998321533203</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A449" s="1">
+        <v>45940</v>
+      </c>
+      <c r="B449">
+        <v>58.900001525878899</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A450" s="1">
+        <v>45943</v>
+      </c>
+      <c r="B450">
+        <v>59.490001678466797</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A451" s="1">
+        <v>45944</v>
+      </c>
+      <c r="B451">
+        <v>58.700000762939403</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A452" s="1">
+        <v>45945</v>
+      </c>
+      <c r="B452">
+        <v>58.270000457763601</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A453" s="1">
+        <v>45946</v>
+      </c>
+      <c r="B453">
+        <v>57.459999084472599</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A454" s="1">
+        <v>45947</v>
+      </c>
+      <c r="B454">
+        <v>57.540000915527301</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A455" s="1">
+        <v>45950</v>
+      </c>
+      <c r="B455">
+        <v>57.520000457763601</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A456" s="1">
+        <v>45951</v>
+      </c>
+      <c r="B456">
+        <v>57.819999694824197</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A457" s="1">
+        <v>45952</v>
+      </c>
+      <c r="B457">
+        <v>58.5</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A458" s="1">
+        <v>45953</v>
+      </c>
+      <c r="B458">
+        <v>61.790000915527301</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A459" s="1">
+        <v>45954</v>
+      </c>
+      <c r="B459">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A460" s="1">
+        <v>45957</v>
+      </c>
+      <c r="B460">
+        <v>61.310001373291001</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A461" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B461">
+        <v>60.150001525878899</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A462" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B462">
+        <v>60.4799995422363</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A463" s="1">
+        <v>45960</v>
+      </c>
+      <c r="B463">
+        <v>60.569999694824197</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A464" s="1">
+        <v>45961</v>
+      </c>
+      <c r="B464">
+        <v>60.9799995422363</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A465" s="1">
+        <v>45964</v>
+      </c>
+      <c r="B465">
+        <v>61.049999237060497</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A466" s="1">
+        <v>45965</v>
+      </c>
+      <c r="B466">
+        <v>60.560001373291001</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A467" s="1">
+        <v>45966</v>
+      </c>
+      <c r="B467">
+        <v>59.599998474121001</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A468" s="1">
+        <v>45967</v>
+      </c>
+      <c r="B468">
+        <v>59.430000305175703</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A469" s="1">
+        <v>45968</v>
+      </c>
+      <c r="B469">
+        <v>59.75</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A470" s="1">
+        <v>45971</v>
+      </c>
+      <c r="B470">
+        <v>60.130001068115199</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A471" s="1">
+        <v>45972</v>
+      </c>
+      <c r="B471">
+        <v>61.040000915527301</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A472" s="1">
+        <v>45973</v>
+      </c>
+      <c r="B472">
+        <v>58.490001678466797</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A473" s="1">
+        <v>45974</v>
+      </c>
+      <c r="B473">
+        <v>58.689998626708899</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A474" s="1">
+        <v>45975</v>
+      </c>
+      <c r="B474">
+        <v>60.090000152587798</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A475" s="1">
+        <v>45978</v>
+      </c>
+      <c r="B475">
+        <v>59.909999847412102</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A476" s="1">
+        <v>45979</v>
+      </c>
+      <c r="B476">
+        <v>60.740001678466797</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A477" s="1">
+        <v>45980</v>
+      </c>
+      <c r="B477">
+        <v>59.439998626708899</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A478" s="1">
+        <v>45981</v>
+      </c>
+      <c r="B478">
+        <v>59.139999389648402</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A479" s="1">
+        <v>45982</v>
+      </c>
+      <c r="B479">
+        <v>58.060001373291001</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A480" s="1">
+        <v>45985</v>
+      </c>
+      <c r="B480">
+        <v>58.840000152587798</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A481" s="1">
+        <v>45986</v>
+      </c>
+      <c r="B481">
+        <v>57.950000762939403</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A482" s="1">
+        <v>45987</v>
+      </c>
+      <c r="B482">
+        <v>58.650001525878899</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A483" s="1">
+        <v>45989</v>
+      </c>
+      <c r="B483">
+        <v>58.549999237060497</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A484" s="1">
+        <v>45992</v>
+      </c>
+      <c r="B484">
+        <v>59.319999694824197</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A485" s="1">
+        <v>45993</v>
+      </c>
+      <c r="B485">
+        <v>58.639999389648402</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A486" s="1">
+        <v>45994</v>
+      </c>
+      <c r="B486">
+        <v>58.950000762939403</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A487" s="1">
+        <v>45995</v>
+      </c>
+      <c r="B487">
+        <v>59.669998168945298</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A488" s="1">
+        <v>45996</v>
+      </c>
+      <c r="B488">
+        <v>60.080001831054602</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A489" s="1">
+        <v>45999</v>
+      </c>
+      <c r="B489">
+        <v>58.880001068115199</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A490" s="1">
+        <v>46000</v>
+      </c>
+      <c r="B490">
+        <v>58.25</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A491" s="1">
+        <v>46001</v>
+      </c>
+      <c r="B491">
+        <v>58.459999084472599</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A492" s="1">
+        <v>46002</v>
+      </c>
+      <c r="B492">
+        <v>57.599998474121001</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A493" s="1">
+        <v>46003</v>
+      </c>
+      <c r="B493">
+        <v>57.439998626708899</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A494" s="1">
+        <v>46006</v>
+      </c>
+      <c r="B494">
+        <v>56.819999694824197</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A495" s="1">
+        <v>46007</v>
+      </c>
+      <c r="B495">
+        <v>55.270000457763601</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A496" s="1">
+        <v>46008</v>
+      </c>
+      <c r="B496">
+        <v>55.939998626708899</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A497" s="1">
+        <v>46009</v>
+      </c>
+      <c r="B497">
+        <v>56.150001525878899</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A498" s="1">
+        <v>46010</v>
+      </c>
+      <c r="B498">
+        <v>56.659999847412102</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A499" s="1">
+        <v>46013</v>
+      </c>
+      <c r="B499">
+        <v>58.009998321533203</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A500" s="1">
+        <v>46014</v>
+      </c>
+      <c r="B500">
+        <v>58.380001068115199</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A501" s="1">
+        <v>46015</v>
+      </c>
+      <c r="B501">
+        <v>58.349998474121001</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>